--- a/data/hex_xlsx/HONBS.HE.xlsx
+++ b/data/hex_xlsx/HONBS.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="465">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -883,6 +883,9 @@
   </si>
   <si>
     <t>Financial liabilities</t>
+  </si>
+  <si>
+    <t>MFI loans LT</t>
   </si>
   <si>
     <t>Loans from related party</t>
@@ -12495,13 +12498,34 @@
       <c r="N79" s="15">
         <v>132.18</v>
       </c>
-      <c r="O79" s="16"/>
-      <c r="P79" s="16"/>
-      <c r="Q79" s="16"/>
-      <c r="R79" s="16"/>
-      <c r="S79" s="16"/>
-      <c r="T79" s="16"/>
-      <c r="U79" s="16"/>
+      <c r="O79" s="15">
+        <f t="shared" ref="O79:U79" si="1">SUM(O53:O57)+O75</f>
+        <v>106.9</v>
+      </c>
+      <c r="P79" s="15">
+        <f t="shared" si="1"/>
+        <v>147.04</v>
+      </c>
+      <c r="Q79" s="15">
+        <f t="shared" si="1"/>
+        <v>167.94</v>
+      </c>
+      <c r="R79" s="15">
+        <f t="shared" si="1"/>
+        <v>201.36</v>
+      </c>
+      <c r="S79" s="15">
+        <f t="shared" si="1"/>
+        <v>252.14</v>
+      </c>
+      <c r="T79" s="15">
+        <f t="shared" si="1"/>
+        <v>196.98</v>
+      </c>
+      <c r="U79" s="15">
+        <f t="shared" si="1"/>
+        <v>209.13</v>
+      </c>
       <c r="V79" s="15">
         <v>228.89</v>
       </c>
@@ -13559,15 +13583,33 @@
       <c r="N105" s="17">
         <v>14.27</v>
       </c>
-      <c r="O105" s="16"/>
-      <c r="P105" s="16"/>
-      <c r="Q105" s="16"/>
-      <c r="R105" s="16"/>
-      <c r="S105" s="16"/>
-      <c r="T105" s="16"/>
-      <c r="U105" s="16"/>
-      <c r="V105" s="16"/>
-      <c r="W105" s="16"/>
+      <c r="O105" s="17">
+        <v>17.52</v>
+      </c>
+      <c r="P105" s="17">
+        <v>35.5</v>
+      </c>
+      <c r="Q105" s="17">
+        <v>25.86</v>
+      </c>
+      <c r="R105" s="17">
+        <v>32.42</v>
+      </c>
+      <c r="S105" s="17">
+        <v>16.18</v>
+      </c>
+      <c r="T105" s="17">
+        <v>17.34</v>
+      </c>
+      <c r="U105" s="17">
+        <v>29.15</v>
+      </c>
+      <c r="V105" s="17">
+        <v>43.28</v>
+      </c>
+      <c r="W105" s="17">
+        <v>25.25</v>
+      </c>
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
@@ -14447,8 +14489,8 @@
       <c r="W124" s="16"/>
     </row>
     <row r="125" ht="15.0" customHeight="1">
-      <c r="A125" s="14" t="s">
-        <v>269</v>
+      <c r="A125" s="21" t="s">
+        <v>288</v>
       </c>
       <c r="B125" s="16"/>
       <c r="C125" s="17">
@@ -14495,7 +14537,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B126" s="16"/>
       <c r="C126" s="16"/>
@@ -14581,7 +14623,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B128" s="16"/>
       <c r="C128" s="16"/>
@@ -14610,7 +14652,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B129" s="16"/>
       <c r="C129" s="16"/>
@@ -14651,7 +14693,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B130" s="16"/>
       <c r="C130" s="16"/>
@@ -14785,7 +14827,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B132" s="16"/>
       <c r="C132" s="17">
@@ -14820,7 +14862,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B133" s="16"/>
       <c r="C133" s="16"/>
@@ -14873,7 +14915,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B134" s="16"/>
       <c r="C134" s="16"/>
@@ -14902,7 +14944,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B135" s="16"/>
       <c r="C135" s="16"/>
@@ -14933,7 +14975,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B136" s="16"/>
       <c r="C136" s="16"/>
@@ -14968,7 +15010,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="18" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B137" s="22"/>
       <c r="C137" s="24">
@@ -15037,7 +15079,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B138" s="16"/>
       <c r="C138" s="16"/>
@@ -15068,7 +15110,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B139" s="16"/>
       <c r="C139" s="16"/>
@@ -15101,7 +15143,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="18" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B140" s="19">
         <v>145.31</v>
@@ -15172,7 +15214,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B141" s="15">
         <v>116.96</v>
@@ -15243,7 +15285,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B142" s="17">
         <v>5.91</v>
@@ -15314,7 +15356,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B143" s="17">
         <v>49.62</v>
@@ -15383,7 +15425,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B144" s="20">
         <v>-14.18</v>
@@ -15436,7 +15478,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B145" s="17">
         <v>1.18</v>
@@ -15497,7 +15539,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B146" s="20">
         <v>-47.26</v>
@@ -15568,7 +15610,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B147" s="16"/>
       <c r="C147" s="16"/>
@@ -15613,7 +15655,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B148" s="16"/>
       <c r="C148" s="16"/>
@@ -15642,7 +15684,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B149" s="16"/>
       <c r="C149" s="17">
@@ -15683,7 +15725,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="18" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B150" s="22"/>
       <c r="C150" s="19">
@@ -15752,7 +15794,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B151" s="16"/>
       <c r="C151" s="16">
@@ -15821,7 +15863,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="18" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B152" s="22"/>
       <c r="C152" s="22">
@@ -15890,7 +15932,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="18" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B153" s="19">
         <v>113.41</v>
@@ -15961,7 +16003,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B154" s="16"/>
       <c r="C154" s="16"/>
@@ -16002,7 +16044,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="18" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B155" s="19">
         <v>257.55</v>
@@ -16073,7 +16115,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B156" s="16"/>
       <c r="C156" s="16"/>
@@ -16102,7 +16144,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B157" s="16"/>
       <c r="C157" s="17">
@@ -16171,7 +16213,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B158" s="16"/>
       <c r="C158" s="17">
@@ -16240,7 +16282,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B159" s="16"/>
       <c r="C159" s="17">
@@ -16309,7 +16351,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B160" s="16"/>
       <c r="C160" s="16"/>
@@ -16342,7 +16384,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B161" s="16"/>
       <c r="C161" s="16"/>
@@ -16375,7 +16417,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B162" s="16"/>
       <c r="C162" s="16"/>
@@ -16412,7 +16454,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B163" s="16"/>
       <c r="C163" s="17">
@@ -16469,7 +16511,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B164" s="16"/>
       <c r="C164" s="17">
@@ -16526,7 +16568,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B165" s="16"/>
       <c r="C165" s="17">
@@ -16581,7 +16623,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B166" s="16"/>
       <c r="C166" s="17">
@@ -16636,7 +16678,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B167" s="16"/>
       <c r="C167" s="16"/>
@@ -16677,7 +16719,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B168" s="16"/>
       <c r="C168" s="16"/>
@@ -16730,7 +16772,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B169" s="16"/>
       <c r="C169" s="16"/>
@@ -16781,7 +16823,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B170" s="16"/>
       <c r="C170" s="17">
@@ -16838,7 +16880,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B171" s="16"/>
       <c r="C171" s="17">
@@ -16895,7 +16937,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B172" s="16"/>
       <c r="C172" s="17">
@@ -16952,7 +16994,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B173" s="16"/>
       <c r="C173" s="17">
@@ -17005,7 +17047,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B174" s="16"/>
       <c r="C174" s="17">
@@ -17048,7 +17090,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B175" s="16"/>
       <c r="C175" s="17">
@@ -17079,7 +17121,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B176" s="16"/>
       <c r="C176" s="16"/>
@@ -17120,7 +17162,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B177" s="16"/>
       <c r="C177" s="17">
@@ -17189,7 +17231,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B178" s="16"/>
       <c r="C178" s="17">
@@ -17258,7 +17300,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B179" s="16"/>
       <c r="C179" s="17">
@@ -17327,7 +17369,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B180" s="16"/>
       <c r="C180" s="17">
@@ -17396,7 +17438,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B181" s="16"/>
       <c r="C181" s="17">
@@ -17465,7 +17507,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B182" s="16"/>
       <c r="C182" s="17">
@@ -17534,7 +17576,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B183" s="16"/>
       <c r="C183" s="17">
@@ -18439,7 +18481,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -18825,70 +18867,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -18964,7 +19006,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -19062,7 +19104,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="20">
@@ -19131,7 +19173,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="17">
@@ -19200,7 +19242,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="17">
@@ -19245,7 +19287,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="20">
@@ -19325,7 +19367,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -19358,7 +19400,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="20">
@@ -19399,7 +19441,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16">
@@ -19430,7 +19472,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="20">
@@ -19469,7 +19511,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="17">
@@ -19538,7 +19580,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="20">
@@ -19569,7 +19611,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -19624,7 +19666,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="20">
@@ -19693,7 +19735,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="17">
@@ -19762,7 +19804,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="17">
@@ -19831,7 +19873,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="20">
@@ -19900,7 +19942,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -19943,7 +19985,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="20">
@@ -20012,7 +20054,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="17">
@@ -20081,7 +20123,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="20">
@@ -20148,7 +20190,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="17">
@@ -20199,7 +20241,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="16">
@@ -20256,7 +20298,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
@@ -20285,7 +20327,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B43" s="20">
         <v>-4.68</v>
@@ -20316,7 +20358,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B44" s="16"/>
       <c r="C44" s="17">
@@ -20355,7 +20397,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B45" s="16"/>
       <c r="C45" s="17">
@@ -20394,7 +20436,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B46" s="16"/>
       <c r="C46" s="17">
@@ -20431,7 +20473,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -20460,7 +20502,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" s="22"/>
       <c r="C48" s="23">
@@ -20529,7 +20571,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -20568,7 +20610,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="17">
@@ -20603,7 +20645,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="20">
@@ -20672,7 +20714,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B52" s="16"/>
       <c r="C52" s="20">
@@ -20741,7 +20783,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B53" s="16"/>
       <c r="C53" s="17">
@@ -20810,7 +20852,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -20849,7 +20891,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
@@ -20884,7 +20926,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -20919,7 +20961,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B57" s="20">
         <v>-14.04</v>
@@ -20950,7 +20992,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="20">
@@ -20985,7 +21027,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B59" s="22"/>
       <c r="C59" s="23">
@@ -21054,7 +21096,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -21095,7 +21137,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B61" s="16">
         <v>0.0</v>
@@ -21154,7 +21196,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
@@ -21209,7 +21251,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -21240,7 +21282,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B64" s="20">
         <v>-4.68</v>
@@ -21283,7 +21325,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -21314,7 +21356,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B66" s="20">
         <v>-4.68</v>
@@ -21385,7 +21427,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="16"/>
@@ -21418,7 +21460,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B68" s="17">
         <v>28.09</v>
@@ -21449,7 +21491,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B69" s="16">
         <v>0.0</v>
@@ -21498,7 +21540,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="20">
@@ -21541,7 +21583,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
@@ -21570,7 +21612,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -21609,7 +21651,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -21640,7 +21682,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
@@ -21669,7 +21711,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="18" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B75" s="23">
         <v>-9.36</v>
@@ -21740,7 +21782,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B76" s="17">
         <v>59.07</v>
@@ -21811,7 +21853,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B77" s="20">
         <v>-1.17</v>
@@ -21852,7 +21894,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B78" s="17">
         <v>29.54</v>
@@ -21923,7 +21965,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B79" s="16"/>
       <c r="C79" s="17">
@@ -21956,7 +21998,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="18" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B80" s="22"/>
       <c r="C80" s="23">
@@ -22964,7 +23006,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23134,22 +23176,22 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -23582,7 +23624,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -23680,27 +23722,27 @@
         <v>70</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="26" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="27"/>
@@ -23732,7 +23774,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="28" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B21" s="29">
         <v>163.94</v>
@@ -23818,7 +23860,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="28" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B22" s="29">
         <v>245.4</v>
@@ -23896,7 +23938,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B23" s="27"/>
       <c r="C23" s="27"/>
@@ -23928,7 +23970,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B24" s="29">
         <v>169.57</v>
@@ -24014,7 +24056,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="28" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B25" s="29">
         <v>304.87</v>
@@ -24092,7 +24134,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="27"/>
@@ -24124,7 +24166,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="28" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B27" s="30">
         <v>27.3</v>
@@ -24210,7 +24252,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="28" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B28" s="30">
         <v>49.08</v>
@@ -24288,7 +24330,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="26" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
@@ -24320,7 +24362,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="28" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B30" s="32">
         <v>-11.52</v>
@@ -24406,7 +24448,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="28" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B31" s="33">
         <v>4.79</v>
@@ -24484,7 +24526,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="26" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B32" s="27"/>
       <c r="C32" s="27"/>
@@ -24516,7 +24558,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="28" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B33" s="33">
         <v>3.88</v>
@@ -24598,7 +24640,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="28" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B34" s="33">
         <v>4.27</v>
@@ -24664,7 +24706,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="28" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B35" s="33">
         <v>3.88</v>
@@ -24750,7 +24792,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B36" s="33">
         <v>4.27</v>
@@ -24828,7 +24870,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="26" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B37" s="27"/>
       <c r="C37" s="27"/>
@@ -24860,7 +24902,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="28" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B38" s="30">
         <v>1.0</v>
@@ -24946,7 +24988,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="28" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B39" s="30">
         <v>1.54</v>
@@ -25024,7 +25066,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="26" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B40" s="27"/>
       <c r="C40" s="27"/>
@@ -25056,7 +25098,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="28" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B41" s="30">
         <v>1.06</v>
@@ -25142,7 +25184,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B42" s="30">
         <v>1.6</v>
@@ -25220,7 +25262,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="26" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B43" s="27"/>
       <c r="C43" s="27"/>
@@ -25252,7 +25294,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="28" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B44" s="30">
         <v>0.37</v>
@@ -25338,7 +25380,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="28" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B45" s="30">
         <v>0.44</v>
@@ -25416,7 +25458,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="26" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B46" s="27"/>
       <c r="C46" s="27"/>
@@ -25448,7 +25490,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="28" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
@@ -25512,7 +25554,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="28" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B48" s="30">
         <v>20.9</v>
@@ -25580,7 +25622,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="26" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B49" s="27"/>
       <c r="C49" s="27"/>
@@ -25612,7 +25654,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="28" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B50" s="29">
         <v>150.16</v>
@@ -25694,7 +25736,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="28" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B51" s="30">
         <v>7.15</v>
@@ -25772,7 +25814,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="26" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B52" s="27"/>
       <c r="C52" s="27"/>
@@ -25804,7 +25846,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="28" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B53" s="31"/>
       <c r="C53" s="31"/>
@@ -25864,7 +25906,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="28" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B54" s="30">
         <v>18.84</v>
@@ -25916,7 +25958,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="26" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B55" s="27"/>
       <c r="C55" s="27"/>
@@ -25948,7 +25990,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="28" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B56" s="31"/>
       <c r="C56" s="31"/>
@@ -26008,7 +26050,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="28" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B57" s="30">
         <v>1.54</v>
@@ -26086,7 +26128,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="26" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B58" s="27"/>
       <c r="C58" s="27"/>
@@ -26118,7 +26160,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="28" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B59" s="31"/>
       <c r="C59" s="31"/>
@@ -26176,7 +26218,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="28" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B60" s="31"/>
       <c r="C60" s="31"/>
@@ -26214,7 +26256,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B61" s="27"/>
       <c r="C61" s="27"/>
@@ -26246,7 +26288,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="28" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B62" s="30">
         <v>0.38</v>
@@ -26332,7 +26374,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="28" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B63" s="30">
         <v>0.37</v>
@@ -26410,7 +26452,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="26" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B64" s="27"/>
       <c r="C64" s="27"/>
@@ -26442,7 +26484,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="28" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B65" s="31"/>
       <c r="C65" s="30">
@@ -26526,7 +26568,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="28" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B66" s="30">
         <v>5.47</v>
@@ -26604,7 +26646,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="26" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B67" s="27"/>
       <c r="C67" s="27"/>
@@ -26636,7 +26678,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="28" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B68" s="31"/>
       <c r="C68" s="31"/>
@@ -26714,7 +26756,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="28" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B69" s="30">
         <v>6.88</v>
@@ -26792,7 +26834,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="26" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B70" s="27"/>
       <c r="C70" s="27"/>
@@ -26824,7 +26866,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="28" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B71" s="31"/>
       <c r="C71" s="31"/>
@@ -26888,7 +26930,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="28" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B72" s="30">
         <v>17.84</v>
